--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,589 +808,589 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9957,0.0002,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0096,0.0000,0.0001,0.9981</t>
-  </si>
-  <si>
-    <t>0.9985,0.0000,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.6318,0.0001,0.0047,0.3817</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0084,0.0000,0.0002,0.9975</t>
+  </si>
+  <si>
+    <t>0.9940,0.0005,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.3987,0.0002,0.0072,0.6842</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8359,0.0001,0.2275,0.0001</t>
-  </si>
-  <si>
-    <t>0.0089,0.0022,0.9903,0.0001</t>
-  </si>
-  <si>
-    <t>0.0647,0.0011,0.9554,0.0000</t>
-  </si>
-  <si>
-    <t>0.0507,0.0005,0.9615,0.0002</t>
-  </si>
-  <si>
-    <t>0.9855,0.0001,0.0318,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9977,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.0146,0.9722,0.0256,0.0002</t>
-  </si>
-  <si>
-    <t>0.0344,0.9675,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0078,0.9889,0.0067,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.9396,0.0007,0.0543,0.0004</t>
-  </si>
-  <si>
-    <t>0.3458,0.0035,0.5212,0.0194</t>
-  </si>
-  <si>
-    <t>0.0017,0.0005,0.9974,0.0005</t>
-  </si>
-  <si>
-    <t>0.2246,0.0005,0.7753,0.0019</t>
-  </si>
-  <si>
-    <t>0.4531,0.0001,0.6862,0.0000</t>
-  </si>
-  <si>
-    <t>0.0108,0.0000,0.9844,0.0026</t>
-  </si>
-  <si>
-    <t>0.0097,0.0001,0.9849,0.0033</t>
-  </si>
-  <si>
-    <t>0.1904,0.6884,0.0455,0.0006</t>
-  </si>
-  <si>
-    <t>0.8203,0.0102,0.1611,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9997,0.0012</t>
-  </si>
-  <si>
-    <t>0.0062,0.9878,0.0064,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0001,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9601,0.0001,0.0605,0.0007</t>
-  </si>
-  <si>
-    <t>0.9958,0.0031,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0077,0.9860,0.0275,0.0002</t>
-  </si>
-  <si>
-    <t>0.0095,0.9526,0.0825,0.0042</t>
-  </si>
-  <si>
-    <t>0.0050,0.0044,0.9529,0.0400</t>
-  </si>
-  <si>
-    <t>0.0006,0.7720,0.9795,0.0006</t>
-  </si>
-  <si>
-    <t>0.0079,0.0004,0.9329,0.0580</t>
-  </si>
-  <si>
-    <t>0.0002,0.3303,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0056,0.9957,0.0030</t>
-  </si>
-  <si>
-    <t>0.6471,0.0048,0.0363,0.2473</t>
-  </si>
-  <si>
-    <t>0.0006,0.9993,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0572,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0158,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9984,0.0037</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0016,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0079,0.0920,0.9670,0.0047</t>
+    <t>0.9928,0.0000,0.0049,0.0000</t>
+  </si>
+  <si>
+    <t>0.4724,0.0014,0.6825,0.0001</t>
+  </si>
+  <si>
+    <t>0.2384,0.0051,0.7930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0206,0.0035,0.9687,0.0008</t>
+  </si>
+  <si>
+    <t>0.8934,0.0001,0.2249,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9966,0.0113,0.0000</t>
+  </si>
+  <si>
+    <t>0.0058,0.9862,0.0164,0.0001</t>
+  </si>
+  <si>
+    <t>0.0424,0.9606,0.0064,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9971,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.7619,0.0003,0.2544,0.0010</t>
+  </si>
+  <si>
+    <t>0.3665,0.0444,0.4890,0.0053</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.1530,0.0002,0.7860,0.0074</t>
+  </si>
+  <si>
+    <t>0.8462,0.0000,0.2893,0.0000</t>
+  </si>
+  <si>
+    <t>0.6764,0.0001,0.4276,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0001,0.9910,0.0071</t>
+  </si>
+  <si>
+    <t>0.8581,0.1058,0.0159,0.0002</t>
+  </si>
+  <si>
+    <t>0.8443,0.0014,0.2209,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.2902,0.4091,0.0576,0.0007</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.9336,0.0001,0.0957,0.0013</t>
+  </si>
+  <si>
+    <t>0.9826,0.0130,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.9870,0.0163,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.9807,0.0415,0.0019</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9223,0.1283</t>
+  </si>
+  <si>
+    <t>0.0034,0.2840,0.9710,0.0013</t>
+  </si>
+  <si>
+    <t>0.4180,0.0005,0.5787,0.0022</t>
+  </si>
+  <si>
+    <t>0.0026,0.2029,0.9857,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9973,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9994,0.0024</t>
+  </si>
+  <si>
+    <t>0.3814,0.0448,0.1436,0.2786</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0055,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0282,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1534,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.0560,0.9706,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9970,0.0072</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0312,0.9965,0.0036</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0003,0.9993,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9787,0.9764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.4185,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0183,0.9972,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0241,0.9496,0.0499,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7120,0.0002,0.5186,0.0001</t>
-  </si>
-  <si>
-    <t>0.8460,0.0050,0.1786,0.0003</t>
-  </si>
-  <si>
-    <t>0.0086,0.0003,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9723,0.7345,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9683,0.9110,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0052,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9161,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.0002,0.9984</t>
+    <t>0.0114,0.0003,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9831,0.9884,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2029,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0843,0.9967,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9892,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0198,0.9713,0.0070,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9988,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.7733,0.0001,0.4318,0.0001</t>
+  </si>
+  <si>
+    <t>0.4542,0.0104,0.5061,0.0006</t>
+  </si>
+  <si>
+    <t>0.0536,0.0003,0.9793,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9840,0.7949,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.8857,0.8380,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0108,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9950,0.6236,0.0002</t>
+  </si>
+  <si>
+    <t>0.0049,0.0000,0.0008,0.9970</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0062,0.0000,0.0000,0.9989</t>
+  </si>
+  <si>
+    <t>0.1025,0.0001,0.0053,0.8990</t>
+  </si>
+  <si>
+    <t>0.0307,0.0001,0.0003,0.9907</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.7395,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9785,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9665,0.4391,0.0028</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9853,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9945,0.2318,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0022</t>
+  </si>
+  <si>
+    <t>0.0044,0.0055,0.9933,0.0005</t>
+  </si>
+  <si>
+    <t>0.9662,0.0009,0.0174,0.0005</t>
+  </si>
+  <si>
+    <t>0.0126,0.0002,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.9931,0.0036,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.8889,0.1012,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.2320,0.6729,0.0421,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9979,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0035,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.7581,0.0030,0.2852,0.0003</t>
+  </si>
+  <si>
+    <t>0.7037,0.0003,0.4129,0.0001</t>
+  </si>
+  <si>
+    <t>0.8756,0.0061,0.1140,0.0005</t>
+  </si>
+  <si>
+    <t>0.7792,0.0041,0.1889,0.0013</t>
+  </si>
+  <si>
+    <t>0.1456,0.0090,0.1174,0.5909</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0063,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9707,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.9898,0.0079,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0019,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9885,0.9769,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6666,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0154,0.9912,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.0250,0.9944,0.0003</t>
+  </si>
+  <si>
+    <t>0.9890,0.0001,0.0093,0.0001</t>
+  </si>
+  <si>
+    <t>0.6460,0.0002,0.4519,0.0002</t>
+  </si>
+  <si>
+    <t>0.2101,0.0000,0.8543,0.0002</t>
+  </si>
+  <si>
+    <t>0.9833,0.0001,0.0135,0.0000</t>
+  </si>
+  <si>
+    <t>0.8643,0.0000,0.0002,0.2515</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0005,0.0000,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0010,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.1836,0.0001,0.0111,0.7966</t>
-  </si>
-  <si>
-    <t>0.0112,0.0001,0.0003,0.9961</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0001,0.9981,0.0829,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9936,0.8233,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9338,0.7324,0.0029</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9910,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9866,0.3897,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9992,0.0030</t>
-  </si>
-  <si>
-    <t>0.2548,0.0016,0.8475,0.0004</t>
-  </si>
-  <si>
-    <t>0.9592,0.0008,0.0384,0.0005</t>
-  </si>
-  <si>
-    <t>0.0370,0.0001,0.9798,0.0001</t>
-  </si>
-  <si>
-    <t>0.0153,0.9857,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0115,0.9858,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.8956,0.0786,0.0087,0.0005</t>
-  </si>
-  <si>
-    <t>0.5175,0.4544,0.0157,0.0003</t>
-  </si>
-  <si>
-    <t>0.0108,0.9866,0.0092,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9845,0.0185,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9306,0.0006,0.0773,0.0005</t>
-  </si>
-  <si>
-    <t>0.9317,0.0007,0.0805,0.0002</t>
-  </si>
-  <si>
-    <t>0.5457,0.0137,0.3329,0.0027</t>
-  </si>
-  <si>
-    <t>0.9176,0.0036,0.0677,0.0006</t>
-  </si>
-  <si>
-    <t>0.0279,0.0106,0.0224,0.9498</t>
-  </si>
-  <si>
-    <t>0.0002,0.9987,0.0408,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9368,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.9945,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9672,0.0232,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0030,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9835,0.9710,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8548,0.9937,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.0548,0.9822,0.0003</t>
-  </si>
-  <si>
-    <t>0.0189,0.0072,0.9642,0.0008</t>
-  </si>
-  <si>
-    <t>0.9558,0.0001,0.0514,0.0003</t>
-  </si>
-  <si>
-    <t>0.6843,0.0016,0.4041,0.0005</t>
-  </si>
-  <si>
-    <t>0.5061,0.0002,0.6247,0.0004</t>
-  </si>
-  <si>
-    <t>0.9485,0.0001,0.0720,0.0001</t>
-  </si>
-  <si>
-    <t>0.8569,0.0001,0.0009,0.1645</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.0000,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9361,0.0000</t>
-  </si>
-  <si>
-    <t>0.0162,0.9750,0.0082,0.0004</t>
-  </si>
-  <si>
-    <t>0.9883,0.0081,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0000,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.0043,0.0010,0.9926,0.0040</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.2956,0.3482,0.1914,0.0013</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0002,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.5424,0.0566,0.1952,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.9874,0.0013,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.9841,0.0114,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9932,0.0030,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9877,0.0109,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9705,0.0012,0.0329,0.0007</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.2486,0.9866,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0788,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0003,0.9983,0.0010</t>
-  </si>
-  <si>
-    <t>0.0149,0.0012,0.9834,0.0001</t>
-  </si>
-  <si>
-    <t>0.0520,0.0007,0.9578,0.0002</t>
-  </si>
-  <si>
-    <t>0.8548,0.0149,0.1062,0.0004</t>
-  </si>
-  <si>
-    <t>0.1160,0.0134,0.8818,0.0002</t>
-  </si>
-  <si>
-    <t>0.0132,0.0990,0.9332,0.0002</t>
-  </si>
-  <si>
-    <t>0.6679,0.0004,0.5330,0.0000</t>
-  </si>
-  <si>
-    <t>0.6981,0.0007,0.3776,0.0003</t>
-  </si>
-  <si>
-    <t>0.2162,0.0003,0.8536,0.0002</t>
-  </si>
-  <si>
-    <t>0.6445,0.4845,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9920,0.0099,0.0004,0.0000</t>
+    <t>0.0170,0.0001,0.0001,0.9952</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.8915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0141,0.9748,0.0124,0.0005</t>
+  </si>
+  <si>
+    <t>0.8308,0.1405,0.0150,0.0006</t>
+  </si>
+  <si>
+    <t>0.9889,0.0000,0.0028,0.0031</t>
+  </si>
+  <si>
+    <t>0.0026,0.0006,0.9955,0.0031</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9643,0.0126,0.0168,0.0006</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.5860,0.0518,0.2343,0.0004</t>
+  </si>
+  <si>
+    <t>0.9803,0.0018,0.0176,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0004,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0020,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0028,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0568,0.0008,0.9591,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0020,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.2583,0.9956,0.0006</t>
+  </si>
+  <si>
+    <t>0.0057,0.0001,0.9950,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0835,0.9951,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0023,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0376,0.0002,0.9712,0.0002</t>
+  </si>
+  <si>
+    <t>0.8632,0.0023,0.1518,0.0003</t>
+  </si>
+  <si>
+    <t>0.6298,0.0018,0.4765,0.0002</t>
+  </si>
+  <si>
+    <t>0.0172,0.0890,0.9481,0.0001</t>
+  </si>
+  <si>
+    <t>0.8932,0.0014,0.1307,0.0001</t>
+  </si>
+  <si>
+    <t>0.6551,0.0003,0.4564,0.0002</t>
+  </si>
+  <si>
+    <t>0.1867,0.0005,0.8650,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0069,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0041,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9968,0.0035,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9734,0.0354,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9162,0.0301,0.0247,0.0003</t>
-  </si>
-  <si>
-    <t>0.9597,0.0001,0.0717,0.0001</t>
-  </si>
-  <si>
-    <t>0.9721,0.0020,0.0055,0.0022</t>
-  </si>
-  <si>
-    <t>0.4161,0.0053,0.5968,0.0031</t>
-  </si>
-  <si>
-    <t>0.5702,0.0130,0.3388,0.0082</t>
-  </si>
-  <si>
-    <t>0.0101,0.0004,0.9859,0.0030</t>
-  </si>
-  <si>
-    <t>0.0005,0.4143,0.9899,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.3946,0.9907,0.0008</t>
-  </si>
-  <si>
-    <t>0.0094,0.0113,0.9774,0.0015</t>
-  </si>
-  <si>
-    <t>0.0089,0.7552,0.3029,0.0078</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.2425,0.0007,0.8373,0.0003</t>
-  </si>
-  <si>
-    <t>0.9626,0.0001,0.0549,0.0005</t>
-  </si>
-  <si>
-    <t>0.0102,0.0002,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0226,0.9926,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0666,0.9982,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0894,0.0006,0.9129,0.0002</t>
+    <t>0.9575,0.0654,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9744,0.0046,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0001,0.0290,0.0001</t>
+  </si>
+  <si>
+    <t>0.9905,0.0007,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.6595,0.0014,0.3954,0.0012</t>
+  </si>
+  <si>
+    <t>0.4500,0.0022,0.6057,0.0026</t>
+  </si>
+  <si>
+    <t>0.0016,0.0010,0.9965,0.0020</t>
+  </si>
+  <si>
+    <t>0.0013,0.0427,0.9834,0.0168</t>
+  </si>
+  <si>
+    <t>0.0049,0.3032,0.9546,0.0044</t>
+  </si>
+  <si>
+    <t>0.1043,0.0075,0.8578,0.0005</t>
+  </si>
+  <si>
+    <t>0.0047,0.1507,0.9520,0.0033</t>
+  </si>
+  <si>
+    <t>0.0020,0.0001,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0519,0.0088,0.9431,0.0011</t>
+  </si>
+  <si>
+    <t>0.9913,0.0001,0.0048,0.0020</t>
+  </si>
+  <si>
+    <t>0.0746,0.0001,0.9547,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0503,0.9939,0.0012</t>
+  </si>
+  <si>
+    <t>0.0030,0.0298,0.9925,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0316,0.0030,0.9595,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.0015,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0132,0.0004,0.9851,0.0005</t>
-  </si>
-  <si>
-    <t>0.0159,0.0002,0.9801,0.0017</t>
-  </si>
-  <si>
-    <t>0.9902,0.0001,0.0059,0.0000</t>
-  </si>
-  <si>
-    <t>0.9699,0.0002,0.0301,0.0003</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.1879,0.9900,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0265,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.5390,0.9780,0.0006</t>
-  </si>
-  <si>
-    <t>0.0060,0.0111,0.9866,0.0008</t>
-  </si>
-  <si>
-    <t>0.0028,0.0001,0.9964,0.0004</t>
-  </si>
-  <si>
-    <t>0.0062,0.0026,0.9820,0.0065</t>
-  </si>
-  <si>
-    <t>0.1122,0.0033,0.8805,0.0005</t>
-  </si>
-  <si>
-    <t>0.1381,0.0047,0.6566,0.0777</t>
-  </si>
-  <si>
-    <t>0.9573,0.0000,0.0020,0.0248</t>
-  </si>
-  <si>
-    <t>0.0088,0.0033,0.0002,0.9952</t>
-  </si>
-  <si>
-    <t>0.6372,0.0002,0.0090,0.1880</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9910,0.0002,0.0016,0.0021</t>
+    <t>0.0005,0.0010,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0009,0.9893,0.0004</t>
+  </si>
+  <si>
+    <t>0.9045,0.0033,0.0549,0.0019</t>
+  </si>
+  <si>
+    <t>0.9814,0.0002,0.0136,0.0000</t>
+  </si>
+  <si>
+    <t>0.9477,0.0001,0.0458,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.3922,0.9677,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0064,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.1496,0.9886,0.0010</t>
+  </si>
+  <si>
+    <t>0.0061,0.0326,0.9771,0.0054</t>
+  </si>
+  <si>
+    <t>0.0794,0.0001,0.9436,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0072,0.9944,0.0098</t>
+  </si>
+  <si>
+    <t>0.7039,0.0029,0.2889,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.0159,0.6488,0.6527</t>
+  </si>
+  <si>
+    <t>0.9873,0.0000,0.0035,0.0037</t>
+  </si>
+  <si>
+    <t>0.0567,0.0025,0.0003,0.9667</t>
+  </si>
+  <si>
+    <t>0.1243,0.0001,0.0067,0.8495</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0003,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1776,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1790,7 +1790,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1804,7 +1804,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1815,10 +1815,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1832,7 +1832,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1846,7 +1846,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1860,7 +1860,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1874,7 +1874,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1888,7 +1888,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1902,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1916,7 +1916,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1930,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1944,7 +1944,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1958,7 +1958,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1972,7 +1972,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1986,7 +1986,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2000,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2014,7 +2014,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2028,7 +2028,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2042,7 +2042,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2056,7 +2056,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2070,7 +2070,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2084,7 +2084,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2095,10 +2095,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2112,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2126,7 +2126,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2137,10 +2137,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2151,10 +2151,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2168,7 +2168,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2179,10 +2179,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2196,7 +2196,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2210,7 +2210,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2221,10 +2221,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2238,7 +2238,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2252,7 +2252,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2266,7 +2266,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2280,7 +2280,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2294,7 +2294,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2308,7 +2308,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2319,10 +2319,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2336,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2350,7 +2350,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2364,7 +2364,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2378,7 +2378,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2389,10 +2389,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2406,7 +2406,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2420,7 +2420,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2434,7 +2434,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2448,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2462,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2476,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2490,7 +2490,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2504,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2518,7 +2518,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2532,7 +2532,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2546,7 +2546,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2560,7 +2560,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2574,7 +2574,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2588,7 +2588,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2602,7 +2602,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2616,7 +2616,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2630,7 +2630,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2644,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2658,7 +2658,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2672,7 +2672,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2686,7 +2686,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2700,7 +2700,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2714,7 +2714,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2725,10 +2725,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2739,10 +2739,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2756,7 +2756,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2770,7 +2770,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2784,7 +2784,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2798,7 +2798,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2812,7 +2812,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2826,7 +2826,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2840,7 +2840,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2854,7 +2854,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2868,7 +2868,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2882,7 +2882,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2896,7 +2896,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2907,10 +2907,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2924,7 +2924,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2938,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2949,10 +2949,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2966,7 +2966,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2980,7 +2980,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2994,7 +2994,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3008,7 +3008,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3022,7 +3022,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3036,7 +3036,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3050,7 +3050,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3064,7 +3064,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3078,7 +3078,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3092,7 +3092,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3106,7 +3106,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3120,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3134,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3148,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3162,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3176,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3190,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3204,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3218,7 +3218,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3232,7 +3232,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3246,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3260,7 +3260,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3274,7 +3274,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3288,7 +3288,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3302,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3313,10 +3313,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3330,7 +3330,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3344,7 +3344,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3358,7 +3358,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3372,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3386,7 +3386,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3400,7 +3400,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3414,7 +3414,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3428,7 +3428,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3442,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3456,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3470,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3484,7 +3484,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3498,7 +3498,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3512,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3526,7 +3526,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3540,7 +3540,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3554,7 +3554,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3568,7 +3568,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3582,7 +3582,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3610,7 +3610,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>312</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3624,7 +3624,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3638,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3652,7 +3652,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3666,7 +3666,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3680,7 +3680,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3694,7 +3694,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3708,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3722,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3736,7 +3736,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3750,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3764,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3778,7 +3778,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3792,7 +3792,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3806,7 +3806,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3820,7 +3820,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3834,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3848,7 +3848,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3862,7 +3862,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3876,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3890,7 +3890,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3904,7 +3904,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3918,7 +3918,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3932,7 +3932,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3946,7 +3946,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3960,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>385</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,7 +4058,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4072,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4086,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4100,7 +4100,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>268</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4114,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4128,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4142,7 +4142,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4156,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4170,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4184,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4198,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4209,10 +4209,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4226,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4240,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4254,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4268,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4282,7 +4282,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4296,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4310,7 +4310,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4324,7 +4324,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4338,7 +4338,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4352,7 +4352,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4366,7 +4366,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4380,7 +4380,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4394,7 +4394,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4408,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4422,7 +4422,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4436,7 +4436,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4447,10 +4447,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4464,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4475,10 +4475,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4492,7 +4492,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4506,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4520,7 +4520,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4534,7 +4534,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4548,7 +4548,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4562,7 +4562,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4576,7 +4576,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4590,7 +4590,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4604,7 +4604,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4618,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4629,10 +4629,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4643,10 +4643,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4660,7 +4660,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4674,7 +4674,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4688,7 +4688,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4702,7 +4702,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4713,10 +4713,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4730,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4744,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4758,7 +4758,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4772,7 +4772,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4786,7 +4786,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>430</v>
+        <v>314</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4800,7 +4800,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4814,7 +4814,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4828,7 +4828,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4993,7 +4993,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
         <v>442</v>
@@ -5038,7 +5038,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5052,7 +5052,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5066,7 +5066,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5080,7 +5080,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5094,7 +5094,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5108,7 +5108,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5122,7 +5122,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>445</v>
+        <v>270</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5136,7 +5136,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5150,7 +5150,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5164,7 +5164,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5175,10 +5175,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5192,7 +5192,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5206,7 +5206,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5220,7 +5220,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5231,10 +5231,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5245,10 +5245,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5262,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5276,7 +5276,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5287,10 +5287,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5304,7 +5304,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5318,7 +5318,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>330</v>
+        <v>457</v>
       </c>
     </row>
     <row r="256" spans="1:4">
